--- a/evaluation_surveys/028_inclusive_assessment_design_survey--evaluation_surveys.xlsx
+++ b/evaluation_surveys/028_inclusive_assessment_design_survey--evaluation_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Educator Roles</t>
+          <t>What roles do educators play in the assessment process?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>How would you describe your experience with the current assessment design?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>strategies</t>
+          <t>ratings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Strategies</t>
+          <t>What would you rate the overall quality of the assessment?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ratings</t>
+          <t>strategies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ratings</t>
+          <t>What strategies do you use when designing assessments?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ratings_2</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ratings</t>
+          <t>What is your feedback on the assessment feedback mechanism?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>How often do you use assessments to inform your work?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>feedback_2</t>
+          <t>diverse_perspectives</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>How would you rate the assessment's ability to capture diverse perspectives?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ratings_3</t>
+          <t>received_feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ratings</t>
+          <t>Have you ever received feedback on your own assessments?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ratings_4</t>
+          <t>received_feedback_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ratings</t>
+          <t>How often do you receive feedback on your assessments?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ratings_5</t>
+          <t>inclusivity_rating</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ratings</t>
+          <t>What rating would you give to the assessment's ability to accommodate different needs?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>experience_2</t>
+          <t>inclusivity_effectiveness</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>How would you rate the assessment's effectiveness in promoting inclusivity?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,90 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>experience_2_2</t>
+          <t>inclusive_strategies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Experience</t>
+          <t>What strategies do you employ when designing assessments to be more inclusive?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>experience_2_3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ratings_6</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ratings</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>experience_3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>lead_educator</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Lead Educator</t>
         </is>
       </c>
     </row>
@@ -918,250 +849,352 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>assistant_educator</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Assistant Educator</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ratings_2_choices</t>
+          <t>educator_roles_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>guest_educator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Guest Educator</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ratings_2_choices</t>
+          <t>educator_roles_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>lead_assistant_educator</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Lead Assistant Educator</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>feedback_2_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>feedback_2_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ratings_4_choices</t>
+          <t>frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ratings_4_choices</t>
+          <t>diverse_perspectives_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Very effective</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ratings_5_choices</t>
+          <t>diverse_perspectives_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Somewhat effective</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ratings_5_choices</t>
+          <t>diverse_perspectives_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>not_effective_at_all</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Not effective at all</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>experience_2_3_choices</t>
+          <t>received_feedback_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>experience_2_3_choices</t>
+          <t>received_feedback_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ratings_6_choices</t>
+          <t>received_feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ratings_6_choices</t>
+          <t>received_feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>experience_3_choices</t>
+          <t>received_feedback_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>experience_3_choices</t>
+          <t>inclusivity_rating_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>inclusivity_rating_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>inclusivity_rating_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>inclusivity_rating_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>inclusivity_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>very_effective</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Very effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>inclusivity_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>somewhat_effective</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Somewhat effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>inclusivity_effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>not_effective_at_all</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Not effective at all</t>
         </is>
       </c>
     </row>
